--- a/data/xlsx/potentielle_de_gonflement.xlsx
+++ b/data/xlsx/potentielle_de_gonflement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJET_ATLAS_MASTER\atlas\data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37343BB9-EE49-41D1-B130-86DE9A774A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE87CDD4-54CE-4D25-98CE-904E4F6FA205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{8711BF94-BCBD-4942-8430-0C41DBBB0764}"/>
   </bookViews>
@@ -2926,6 +2926,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477A8630-F6AB-4615-8B23-B70152D11A80}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="54.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
